--- a/BD_SKUs_Autorizados.xlsx
+++ b/BD_SKUs_Autorizados.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2207"/>
+  <dimension ref="A1:A2208"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15865,6 +15865,13 @@
         </is>
       </c>
     </row>
+    <row r="2208">
+      <c r="A2208" t="inlineStr">
+        <is>
+          <t>S/N</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_SKUs_Autorizados.xlsx
+++ b/BD_SKUs_Autorizados.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2208"/>
+  <dimension ref="A1:A2209"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15872,6 +15872,13 @@
         </is>
       </c>
     </row>
+    <row r="2209">
+      <c r="A2209" t="inlineStr">
+        <is>
+          <t>11-7761-01</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_SKUs_Autorizados.xlsx
+++ b/BD_SKUs_Autorizados.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2209"/>
+  <dimension ref="A1:A2210"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15879,6 +15879,13 @@
         </is>
       </c>
     </row>
+    <row r="2210">
+      <c r="A2210" t="inlineStr">
+        <is>
+          <t>PLACA ENSAMBLE</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
